--- a/sensibilidad_frontera.xlsx
+++ b/sensibilidad_frontera.xlsx
@@ -506,10 +506,10 @@
         <v>50000</v>
       </c>
       <c r="D2">
-        <v>-165.46</v>
+        <v>-0.12</v>
       </c>
       <c r="E2">
-        <v>26.08</v>
+        <v>0.03</v>
       </c>
       <c r="F2" t="s">
         <v>14</v>
@@ -526,13 +526,13 @@
         <v>50050</v>
       </c>
       <c r="D3">
-        <v>-90.36</v>
+        <v>0.19</v>
       </c>
       <c r="E3">
-        <v>-50.5</v>
+        <v>0.27</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -546,13 +546,13 @@
         <v>56050</v>
       </c>
       <c r="D4">
-        <v>58.14</v>
+        <v>-1.84</v>
       </c>
       <c r="E4">
-        <v>0.76</v>
+        <v>-0.97</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -566,13 +566,13 @@
         <v>58350</v>
       </c>
       <c r="D5">
-        <v>103.51</v>
+        <v>-0</v>
       </c>
       <c r="E5">
-        <v>-27.99</v>
+        <v>0.01</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -586,10 +586,10 @@
         <v>56052</v>
       </c>
       <c r="D6">
-        <v>60.71</v>
+        <v>1.83</v>
       </c>
       <c r="E6">
-        <v>-15.35</v>
+        <v>0.98</v>
       </c>
       <c r="F6" t="s">
         <v>15</v>
@@ -606,10 +606,10 @@
         <v>50000</v>
       </c>
       <c r="D7">
-        <v>-158.43</v>
+        <v>-0.15</v>
       </c>
       <c r="E7">
-        <v>43.26</v>
+        <v>-0.03</v>
       </c>
       <c r="F7" t="s">
         <v>14</v>
@@ -626,13 +626,13 @@
         <v>50050</v>
       </c>
       <c r="D8">
-        <v>-88.95</v>
+        <v>0.29</v>
       </c>
       <c r="E8">
-        <v>-40.6</v>
+        <v>0.68</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -646,13 +646,13 @@
         <v>56050</v>
       </c>
       <c r="D9">
-        <v>59.75</v>
+        <v>-4.04</v>
       </c>
       <c r="E9">
-        <v>5.57</v>
+        <v>-2.07</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -666,13 +666,13 @@
         <v>58350</v>
       </c>
       <c r="D10">
-        <v>85.20999999999999</v>
+        <v>-0.02</v>
       </c>
       <c r="E10">
-        <v>-14.32</v>
+        <v>0.01</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -686,10 +686,10 @@
         <v>56052</v>
       </c>
       <c r="D11">
-        <v>66.43000000000001</v>
+        <v>4.02</v>
       </c>
       <c r="E11">
-        <v>-7.95</v>
+        <v>2.08</v>
       </c>
       <c r="F11" t="s">
         <v>15</v>
@@ -706,10 +706,10 @@
         <v>50000</v>
       </c>
       <c r="D12">
-        <v>-165.85</v>
+        <v>-0.15</v>
       </c>
       <c r="E12">
-        <v>51.22</v>
+        <v>-0.06</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
@@ -726,13 +726,13 @@
         <v>50050</v>
       </c>
       <c r="D13">
-        <v>-75.75</v>
+        <v>0.3</v>
       </c>
       <c r="E13">
-        <v>-12.51</v>
+        <v>0.67</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -746,13 +746,13 @@
         <v>56050</v>
       </c>
       <c r="D14">
-        <v>66.17</v>
+        <v>-5.86</v>
       </c>
       <c r="E14">
-        <v>8.31</v>
+        <v>-2.72</v>
       </c>
       <c r="F14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -766,13 +766,13 @@
         <v>58350</v>
       </c>
       <c r="D15">
-        <v>102.55</v>
+        <v>-0.02</v>
       </c>
       <c r="E15">
-        <v>-10.93</v>
+        <v>0.02</v>
       </c>
       <c r="F15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -786,10 +786,10 @@
         <v>56052</v>
       </c>
       <c r="D16">
-        <v>76.17</v>
+        <v>5.84</v>
       </c>
       <c r="E16">
-        <v>-3.28</v>
+        <v>2.73</v>
       </c>
       <c r="F16" t="s">
         <v>15</v>
@@ -845,25 +845,25 @@
         <v>25</v>
       </c>
       <c r="C2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>0.8085</v>
+        <v>0.9697</v>
       </c>
       <c r="E2">
-        <v>1.2541</v>
+        <v>1.0444</v>
       </c>
       <c r="F2">
         <v>719</v>
       </c>
       <c r="G2">
-        <v>478.18</v>
+        <v>3.98</v>
       </c>
       <c r="H2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="J2">
         <v>513</v>
@@ -877,25 +877,25 @@
         <v>26</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D3">
-        <v>0.8114</v>
+        <v>0.9696</v>
       </c>
       <c r="E3">
-        <v>1.2556</v>
+        <v>1.0444</v>
       </c>
       <c r="F3">
-        <v>692.25</v>
+        <v>719.0599999999999</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>513</v>
@@ -909,25 +909,25 @@
         <v>25</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4">
-        <v>0.793</v>
+        <v>0.9624</v>
       </c>
       <c r="E4">
-        <v>1.249</v>
+        <v>1.0527</v>
       </c>
       <c r="F4">
         <v>1199.14</v>
       </c>
       <c r="G4">
-        <v>458.77</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H4">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="J4">
         <v>513</v>
@@ -941,25 +941,25 @@
         <v>26</v>
       </c>
       <c r="C5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5">
-        <v>0.7905</v>
+        <v>0.9624</v>
       </c>
       <c r="E5">
-        <v>1.2481</v>
+        <v>1.0527</v>
       </c>
       <c r="F5">
-        <v>1169.36</v>
+        <v>1199.23</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>513</v>
@@ -973,25 +973,25 @@
         <v>25</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D6">
-        <v>0.7521</v>
+        <v>0.9647</v>
       </c>
       <c r="E6">
-        <v>1.2474</v>
+        <v>1.0467</v>
       </c>
       <c r="F6">
         <v>1244.28</v>
       </c>
       <c r="G6">
-        <v>486.48</v>
+        <v>12.17</v>
       </c>
       <c r="H6">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>513</v>
@@ -1005,25 +1005,25 @@
         <v>26</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>0.7425</v>
+        <v>0.9647</v>
       </c>
       <c r="E7">
-        <v>1.2439</v>
+        <v>1.0466</v>
       </c>
       <c r="F7">
-        <v>1256.51</v>
+        <v>1244.39</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="I7">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>513</v>
@@ -1070,19 +1070,19 @@
         <v>513</v>
       </c>
       <c r="C2">
-        <v>0.0177</v>
+        <v>0.0001</v>
       </c>
       <c r="D2">
-        <v>0.0021</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>58312</v>
+        <v>4412</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1093,19 +1093,19 @@
         <v>513</v>
       </c>
       <c r="C3">
-        <v>0.0194</v>
+        <v>0.0001</v>
       </c>
       <c r="D3">
-        <v>0.0041</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>56060</v>
+        <v>50880</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1116,19 +1116,19 @@
         <v>513</v>
       </c>
       <c r="C4">
-        <v>0.0388</v>
+        <v>0.0001</v>
       </c>
       <c r="D4">
-        <v>0.0131</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>390</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>56060</v>
+        <v>50880</v>
       </c>
     </row>
   </sheetData>
